--- a/apps/web/public/templates/07_كتالوج_المهمات.xlsx
+++ b/apps/web/public/templates/07_كتالوج_المهمات.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,6 +757,18 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>{"المهمات": [["1.1.7", "48 FIBER OPTIC CABLE", "KM", "المصرية للاتصالات", "Supply of F.O. Cables"]]}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/apps/web/public/templates/07_كتالوج_المهمات.xlsx
+++ b/apps/web/public/templates/07_كتالوج_المهمات.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>التوريد</t>
+          <t>جهة التوريد</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="D3:D5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="قيمة غير مسموحة" error="اختار من القائمة" type="list">
+    <dataValidation sqref="D3:D5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="قيمة غير مسموحة" error="يرجى الاختيار من القائمة" type="list">
       <formula1>"المصرية للاتصالات,الشركة المنفذة"</formula1>
     </dataValidation>
   </dataValidations>
@@ -632,21 +632,21 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>قالب كتالوج المهمات</t>
+          <t>نموذج كتالوج المهمات</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>الغرض: تعريف أصناف المهمات (رقم الشطب) اللي بتتصرف من المخازن.</t>
+          <t>الغرض: تعريف أصناف المهمات (رقم الشطب) المنصرفة من المخازن.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>مين بيرفعه: المخازن والمشتريات.</t>
+          <t>الجهة المسؤولة عن الرفع: المخازن والمشتريات.</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>قواعد الملء</t>
+          <t>قواعد تعبئة البيانات</t>
         </is>
       </c>
     </row>
@@ -673,49 +673,49 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>قواعد عامة لكل القوالب</t>
+          <t>قواعد عامة لجميع النماذج</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>• ما تغيّرش أسماء الشيتات ولا ترتيب الأعمدة ولا الصف التاني (اسم العمود التقني).</t>
+          <t>• لا يجوز تغيير أسماء أوراق العمل أو ترتيب الأعمدة أو الصف الثاني (الاسم التقني للعمود).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>• العمود اللي عليه * إلزامي. الأعمدة اللي فيها قائمة لازم تختار منها.</t>
+          <t>• العمود المميز بعلامة * إلزامي، ويجب الاختيار من القائمة في الأعمدة التي تتضمن قائمة اختيار.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>• الصفوف الرمادي أمثلة — امسحها قبل الرفع.</t>
+          <t>• الصفوف الرمادية أمثلة توضيحية — يرجى حذفها قبل الرفع.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>• الأرقام من غير فواصل أو عملة. التواريخ يوم/شهر/سنة.</t>
+          <t>• تُدخل الأرقام دون فواصل أو رمز عملة، والتواريخ بصيغة يوم/شهر/سنة.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>• عند الرفع السيستم بيعرض معاينة بكل صف وأخطاؤه قبل الحفظ — مفيش حاجة بتتحفظ قبل ما توافق.</t>
+          <t>• عند الرفع تعرض المنظومة نتيجة المراجعة لكل صف وأخطاءه قبل الحفظ — ولا يُحفظ أي سجل قبل «اعتماد الاستيراد».</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>• نسخة القالب: 1.0 — لو القالب قديم السيستم هيطلب تنزيل النسخة الجديدة.</t>
+          <t>• إصدار النموذج: 1.0 — إذا كان النموذج قديماً ستطلب المنظومة تحميل الإصدار الأحدث.</t>
         </is>
       </c>
     </row>

--- a/apps/web/public/templates/07_كتالوج_المهمات.xlsx
+++ b/apps/web/public/templates/07_كتالوج_المهمات.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>48 FIBER OPTIC CABLE</t>
+          <t>مثال — 48 FIBER OPTIC CABLE</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{"المهمات": [["1.1.7", "48 FIBER OPTIC CABLE", "KM", "المصرية للاتصالات", "Supply of F.O. Cables"]]}</t>
+          <t>{"المهمات": [["1.1.7", "مثال — 48 FIBER OPTIC CABLE", "KM", "المصرية للاتصالات", "Supply of F.O. Cables"]]}</t>
         </is>
       </c>
     </row>
